--- a/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>NEE</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28114000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20956000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17069000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17997000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19204000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16727000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17173000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16138000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17486000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17021000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15136000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14256000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15341000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10138000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10817000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8480000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7290000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8003000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7060000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7529000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7522000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8588000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8750000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8152000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8276000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9258000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>17976000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10139000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8589000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10707000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11201000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9667000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9644000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8616000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8898000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8271000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6984000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5980000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6083000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-405000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-522000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-77000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1147000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-299000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3964000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-596000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-305000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>28000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>87000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5879000</v>
+      </c>
+      <c r="E15" s="3">
         <v>4503000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3924000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4052000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4216000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3911000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2357000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3120000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2831000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2551000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2163000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1518000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1567000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17877000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16875000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14156000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14381000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13851000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8520000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12000000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11679000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12854000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12637000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11895000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10996000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12116000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10237000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4081000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2913000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3616000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5353000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8207000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5173000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4459000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4632000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4384000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3241000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3260000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3225000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E20" s="3">
         <v>336000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1532000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>747000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>382000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>880000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1212000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>577000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>458000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1458000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>381000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>262000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16763000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9207000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8659000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8678000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9857000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>12736000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8691000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9099000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8412000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7738000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7220000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5054000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3324000</v>
+      </c>
+      <c r="E22" s="3">
         <v>585000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1270000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1950000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1543000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1237000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1390000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1293000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1219000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1197000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2245000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1038000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1035000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7288000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3832000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3175000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2413000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3836000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7352000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4663000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4378000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3990000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3645000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2454000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2603000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2452000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1006000</v>
+      </c>
+      <c r="E24" s="3">
         <v>586000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>348000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-43000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>359000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2012000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1221000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1379000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1228000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1176000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>777000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>692000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>529000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6282000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3246000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2827000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2456000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3477000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5340000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3442000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2999000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2762000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2469000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1677000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1911000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1923000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7310000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4147000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3573000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3006000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3858000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6202000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3499000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2906000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2752000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2465000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1677000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1911000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1923000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1536,39 +1596,42 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3">
         <v>-87000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-89000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>436000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1881000</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>231000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-375000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-336000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1532000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-747000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-382000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-880000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1212000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-577000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-458000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1458000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-381000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-262000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7310000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4147000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3573000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2919000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3769000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6638000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5380000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2906000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2752000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2465000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1908000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1911000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1923000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7310000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4147000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3573000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2919000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3769000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6638000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5380000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2906000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2752000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2465000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1908000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1911000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1923000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2690000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1601000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>639000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1105000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>638000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1714000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1292000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>571000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>577000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>438000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>329000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>377000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1985,278 +2074,299 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6040000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5093000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4108000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2974000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2807000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2969000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2737000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2439000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2265000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2159000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2289000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2056000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1802000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1934000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1561000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1552000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1328000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1223000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1273000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1289000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1259000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1292000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1153000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1073000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1074000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4525000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4862000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2980000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1751000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2673000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1563000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1597000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2389000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2700000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2916000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1962000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1779000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1638000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15361000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13490000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9288000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7382000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7408000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6393000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7181000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7409000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6795000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6944000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5842000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5237000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4872000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14854000</v>
+      </c>
+      <c r="E47" s="3">
         <v>14078000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15081000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13507000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14407000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12634000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10813000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7916000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6924000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6565000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6657000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5166000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4774000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>126612000</v>
+      </c>
+      <c r="E48" s="3">
         <v>111825000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>100100000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>91803000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>82571000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>70535000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72289000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66912000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>61386000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55705000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>52720000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49413000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42490000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8489000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6335000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5586000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4947000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4204000</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>8</v>
@@ -2264,24 +2374,27 @@
       <c r="J49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L49" s="3">
         <v>1842000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>614000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>240000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>247000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>262000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12173000</v>
+      </c>
+      <c r="E52" s="3">
         <v>13207000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10857000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10045000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9101000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14140000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10169000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7756000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5532000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4882000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5789000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4376000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4790000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>177489000</v>
+      </c>
+      <c r="E54" s="3">
         <v>158935000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>140912000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>127684000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117691000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>103702000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97963000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>89993000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82479000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74605000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69306000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64439000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>57188000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8504000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8312000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6935000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4615000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3631000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2386000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3235000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3447000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2529000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1354000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1281000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1191000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11806000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9710000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3867000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6147000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5040000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10930000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3615000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3022000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3006000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4657000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4457000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4182000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2157000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7653000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8673000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6635000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4796000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5182000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4247000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4411000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4450000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4572000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3652000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3532000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3416000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3371000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27963000</v>
+      </c>
+      <c r="E60" s="3">
         <v>26695000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17437000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15558000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13853000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17563000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11243000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10919000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10107000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9663000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9189000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8879000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6719000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61405000</v>
+      </c>
+      <c r="E61" s="3">
         <v>55256000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50960000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41944000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37543000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>26782000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31410000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27818000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26681000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24044000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23969000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23177000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20810000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>29097000</v>
+      </c>
+      <c r="E62" s="3">
         <v>27548000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26846000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25253000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24448000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21476000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25779000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>25925000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22579000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20730000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18108000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16315000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14716000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>130021000</v>
+      </c>
+      <c r="E66" s="3">
         <v>119706000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>103710000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91171000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>80686000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69558000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>69727000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65652000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>59905000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54689000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51266000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48371000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42245000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30235000</v>
+      </c>
+      <c r="E72" s="3">
         <v>26707000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25911000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25363000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25199000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23837000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19020000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15458000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14140000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12773000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11569000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>10783000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9876000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47468000</v>
+      </c>
+      <c r="E76" s="3">
         <v>39229000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>37202000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>36513000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37005000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>34144000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28236000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24341000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22574000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19916000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18040000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16068000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14943000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7310000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4147000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3573000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2919000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3769000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6638000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5380000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2906000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2752000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2465000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1908000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1911000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1923000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6151000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4790000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4214000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4315000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4478000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4147000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2638000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3428000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3203000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2896000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2521000</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1567000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11301000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8262000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7553000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7983000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8155000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6593000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6458000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6369000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6116000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5500000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5102000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3992000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4074000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9548000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9742000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7048000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6747000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5912000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6010000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5445000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4240000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3872000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3503000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3228000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4870000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4027000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23467000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18359000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13591000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13699000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16177000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10950000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8918000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8046000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8005000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6361000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6123000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5279000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3782000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3352000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3024000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2743000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2408000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2101000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1845000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-1612000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1385000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1261000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1122000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1004000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-920000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,77 +4398,83 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12149000</v>
+      </c>
+      <c r="E100" s="3">
         <v>12229000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5807000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6174000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3873000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7634000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2888000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2424000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1883000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1130000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1280000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-20000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>26000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10000</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2125000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-230000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>438000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4145000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3270000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>454000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>757000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>139000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>109000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-48000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>75000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
@@ -977,19 +977,19 @@
         <v>-522000</v>
       </c>
       <c r="F14" s="3">
-        <v>-77000</v>
+        <v>-49000</v>
       </c>
       <c r="G14" s="3">
-        <v>1147000</v>
+        <v>1330000</v>
       </c>
       <c r="H14" s="3">
-        <v>-299000</v>
+        <v>-65000</v>
       </c>
       <c r="I14" s="3">
-        <v>-3964000</v>
+        <v>-3961000</v>
       </c>
       <c r="J14" s="3">
-        <v>-596000</v>
+        <v>659000</v>
       </c>
       <c r="K14" s="3">
         <v>-305000</v>
@@ -1195,7 +1195,7 @@
         <v>1532000</v>
       </c>
       <c r="G20" s="3">
-        <v>747000</v>
+        <v>334000</v>
       </c>
       <c r="H20" s="3">
         <v>26000</v>
@@ -1240,7 +1240,7 @@
         <v>8659000</v>
       </c>
       <c r="G21" s="3">
-        <v>8678000</v>
+        <v>8265000</v>
       </c>
       <c r="H21" s="3">
         <v>9857000</v>
@@ -1285,7 +1285,7 @@
         <v>1270000</v>
       </c>
       <c r="G22" s="3">
-        <v>1950000</v>
+        <v>1537000</v>
       </c>
       <c r="H22" s="3">
         <v>1543000</v>
@@ -1735,7 +1735,7 @@
         <v>-1532000</v>
       </c>
       <c r="G32" s="3">
-        <v>-747000</v>
+        <v>-334000</v>
       </c>
       <c r="H32" s="3">
         <v>-26000</v>

--- a/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>NEE</t>
   </si>
@@ -663,7 +663,8 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -778,16 +779,16 @@
         <v>10817000</v>
       </c>
       <c r="F9" s="3">
-        <v>8480000</v>
+        <v>8508000</v>
       </c>
       <c r="G9" s="3">
-        <v>7290000</v>
+        <v>7473000</v>
       </c>
       <c r="H9" s="3">
         <v>8003000</v>
       </c>
       <c r="I9" s="3">
-        <v>7060000</v>
+        <v>7062000</v>
       </c>
       <c r="J9" s="3">
         <v>7529000</v>
@@ -823,16 +824,16 @@
         <v>10139000</v>
       </c>
       <c r="F10" s="3">
-        <v>8589000</v>
+        <v>8561000</v>
       </c>
       <c r="G10" s="3">
-        <v>10707000</v>
+        <v>10524000</v>
       </c>
       <c r="H10" s="3">
         <v>11201000</v>
       </c>
       <c r="I10" s="3">
-        <v>9667000</v>
+        <v>9665000</v>
       </c>
       <c r="J10" s="3">
         <v>9644000</v>
@@ -971,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-405000</v>
+        <v>-689000</v>
       </c>
       <c r="E14" s="3">
-        <v>-522000</v>
+        <v>-27000</v>
       </c>
       <c r="F14" s="3">
-        <v>-49000</v>
+        <v>-414000</v>
       </c>
       <c r="G14" s="3">
-        <v>1330000</v>
+        <v>-566000</v>
       </c>
       <c r="H14" s="3">
-        <v>-65000</v>
+        <v>-465000</v>
       </c>
       <c r="I14" s="3">
-        <v>-3961000</v>
+        <v>-3926000</v>
       </c>
       <c r="J14" s="3">
-        <v>659000</v>
+        <v>547000</v>
       </c>
       <c r="K14" s="3">
         <v>-305000</v>
@@ -1019,7 +1020,7 @@
         <v>5879000</v>
       </c>
       <c r="E15" s="3">
-        <v>4503000</v>
+        <v>4389000</v>
       </c>
       <c r="F15" s="3">
         <v>3924000</v>
@@ -1077,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17877000</v>
+        <v>18037000</v>
       </c>
       <c r="E17" s="3">
-        <v>16875000</v>
+        <v>17081000</v>
       </c>
       <c r="F17" s="3">
-        <v>14156000</v>
+        <v>13976000</v>
       </c>
       <c r="G17" s="3">
-        <v>14381000</v>
+        <v>13034000</v>
       </c>
       <c r="H17" s="3">
-        <v>13851000</v>
+        <v>13838000</v>
       </c>
       <c r="I17" s="3">
-        <v>8520000</v>
+        <v>12356000</v>
       </c>
       <c r="J17" s="3">
-        <v>12000000</v>
+        <v>11190000</v>
       </c>
       <c r="K17" s="3">
         <v>11679000</v>
@@ -1122,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10237000</v>
+        <v>10077000</v>
       </c>
       <c r="E18" s="3">
-        <v>4081000</v>
+        <v>3875000</v>
       </c>
       <c r="F18" s="3">
-        <v>2913000</v>
+        <v>3093000</v>
       </c>
       <c r="G18" s="3">
-        <v>3616000</v>
+        <v>4963000</v>
       </c>
       <c r="H18" s="3">
-        <v>5353000</v>
+        <v>5366000</v>
       </c>
       <c r="I18" s="3">
-        <v>8207000</v>
+        <v>4371000</v>
       </c>
       <c r="J18" s="3">
-        <v>5173000</v>
+        <v>5983000</v>
       </c>
       <c r="K18" s="3">
         <v>4459000</v>
@@ -1186,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>375000</v>
+        <v>154000</v>
       </c>
       <c r="E20" s="3">
-        <v>336000</v>
+        <v>-515000</v>
       </c>
       <c r="F20" s="3">
-        <v>1532000</v>
+        <v>-938000</v>
       </c>
       <c r="G20" s="3">
-        <v>334000</v>
+        <v>1166000</v>
       </c>
       <c r="H20" s="3">
-        <v>26000</v>
+        <v>-254000</v>
       </c>
       <c r="I20" s="3">
-        <v>382000</v>
+        <v>-502000</v>
       </c>
       <c r="J20" s="3">
-        <v>880000</v>
+        <v>-704000</v>
       </c>
       <c r="K20" s="3">
         <v>1212000</v>
@@ -1231,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>16763000</v>
+        <v>15802000</v>
       </c>
       <c r="E21" s="3">
-        <v>9207000</v>
+        <v>8779000</v>
       </c>
       <c r="F21" s="3">
-        <v>8659000</v>
+        <v>7955000</v>
       </c>
       <c r="G21" s="3">
-        <v>8265000</v>
+        <v>7849000</v>
       </c>
       <c r="H21" s="3">
-        <v>9857000</v>
+        <v>9836000</v>
       </c>
       <c r="I21" s="3">
-        <v>12736000</v>
+        <v>8784000</v>
       </c>
       <c r="J21" s="3">
-        <v>8691000</v>
+        <v>9044000</v>
       </c>
       <c r="K21" s="3">
         <v>9099000</v>
@@ -1285,16 +1286,16 @@
         <v>1270000</v>
       </c>
       <c r="G22" s="3">
-        <v>1537000</v>
+        <v>1950000</v>
       </c>
       <c r="H22" s="3">
-        <v>1543000</v>
+        <v>2249000</v>
       </c>
       <c r="I22" s="3">
-        <v>1237000</v>
+        <v>1498000</v>
       </c>
       <c r="J22" s="3">
-        <v>1390000</v>
+        <v>1558000</v>
       </c>
       <c r="K22" s="3">
         <v>1293000</v>
@@ -1375,16 +1376,16 @@
         <v>348000</v>
       </c>
       <c r="G24" s="3">
-        <v>-43000</v>
+        <v>44000</v>
       </c>
       <c r="H24" s="3">
-        <v>359000</v>
+        <v>448000</v>
       </c>
       <c r="I24" s="3">
-        <v>2012000</v>
+        <v>1576000</v>
       </c>
       <c r="J24" s="3">
-        <v>1221000</v>
+        <v>-660000</v>
       </c>
       <c r="K24" s="3">
         <v>1379000</v>
@@ -1465,16 +1466,16 @@
         <v>2827000</v>
       </c>
       <c r="G26" s="3">
-        <v>2456000</v>
+        <v>2369000</v>
       </c>
       <c r="H26" s="3">
-        <v>3477000</v>
+        <v>3388000</v>
       </c>
       <c r="I26" s="3">
-        <v>5340000</v>
+        <v>5776000</v>
       </c>
       <c r="J26" s="3">
-        <v>3442000</v>
+        <v>5323000</v>
       </c>
       <c r="K26" s="3">
         <v>2999000</v>
@@ -1510,16 +1511,16 @@
         <v>3573000</v>
       </c>
       <c r="G27" s="3">
-        <v>3006000</v>
+        <v>2919000</v>
       </c>
       <c r="H27" s="3">
-        <v>3858000</v>
+        <v>3769000</v>
       </c>
       <c r="I27" s="3">
-        <v>6202000</v>
+        <v>6638000</v>
       </c>
       <c r="J27" s="3">
-        <v>3499000</v>
+        <v>5380000</v>
       </c>
       <c r="K27" s="3">
         <v>2906000</v>
@@ -1590,26 +1591,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-87000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>436000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>1881000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1726,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-375000</v>
+        <v>-154000</v>
       </c>
       <c r="E32" s="3">
-        <v>-336000</v>
+        <v>515000</v>
       </c>
       <c r="F32" s="3">
-        <v>-1532000</v>
+        <v>938000</v>
       </c>
       <c r="G32" s="3">
-        <v>-334000</v>
+        <v>-1166000</v>
       </c>
       <c r="H32" s="3">
-        <v>-26000</v>
+        <v>254000</v>
       </c>
       <c r="I32" s="3">
-        <v>-382000</v>
+        <v>502000</v>
       </c>
       <c r="J32" s="3">
-        <v>-880000</v>
+        <v>704000</v>
       </c>
       <c r="K32" s="3">
         <v>-1212000</v>
@@ -2084,10 +2085,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6040000</v>
+        <v>6607000</v>
       </c>
       <c r="E43" s="3">
-        <v>5093000</v>
+        <v>5436000</v>
       </c>
       <c r="F43" s="3">
         <v>4108000</v>
@@ -2174,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4525000</v>
+        <v>3228000</v>
       </c>
       <c r="E45" s="3">
-        <v>4862000</v>
+        <v>4519000</v>
       </c>
       <c r="F45" s="3">
-        <v>2980000</v>
+        <v>2303000</v>
       </c>
       <c r="G45" s="3">
-        <v>1751000</v>
+        <v>1377000</v>
       </c>
       <c r="H45" s="3">
-        <v>2673000</v>
+        <v>2262000</v>
       </c>
       <c r="I45" s="3">
-        <v>1563000</v>
+        <v>1474000</v>
       </c>
       <c r="J45" s="3">
-        <v>1597000</v>
+        <v>1210000</v>
       </c>
       <c r="K45" s="3">
         <v>2389000</v>
@@ -2264,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>14854000</v>
+        <v>16467000</v>
       </c>
       <c r="E47" s="3">
-        <v>14078000</v>
+        <v>15129000</v>
       </c>
       <c r="F47" s="3">
-        <v>15081000</v>
+        <v>15438000</v>
       </c>
       <c r="G47" s="3">
-        <v>13507000</v>
+        <v>13787000</v>
       </c>
       <c r="H47" s="3">
-        <v>14407000</v>
+        <v>14604000</v>
       </c>
       <c r="I47" s="3">
-        <v>12634000</v>
+        <v>12784000</v>
       </c>
       <c r="J47" s="3">
-        <v>10813000</v>
+        <v>8324000</v>
       </c>
       <c r="K47" s="3">
         <v>7916000</v>
@@ -2312,19 +2313,19 @@
         <v>126612000</v>
       </c>
       <c r="E48" s="3">
-        <v>111825000</v>
+        <v>111823000</v>
       </c>
       <c r="F48" s="3">
         <v>100100000</v>
       </c>
       <c r="G48" s="3">
-        <v>91803000</v>
+        <v>92466000</v>
       </c>
       <c r="H48" s="3">
-        <v>82571000</v>
+        <v>82010000</v>
       </c>
       <c r="I48" s="3">
-        <v>70535000</v>
+        <v>70334000</v>
       </c>
       <c r="J48" s="3">
         <v>72289000</v>
@@ -2354,10 +2355,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>8489000</v>
+        <v>6783000</v>
       </c>
       <c r="E49" s="3">
-        <v>6335000</v>
+        <v>5613000</v>
       </c>
       <c r="F49" s="3">
         <v>5586000</v>
@@ -2366,13 +2367,13 @@
         <v>4947000</v>
       </c>
       <c r="H49" s="3">
-        <v>4204000</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+        <v>4756000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1599000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2051000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -2489,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12173000</v>
+        <v>5739000</v>
       </c>
       <c r="E52" s="3">
-        <v>13207000</v>
+        <v>5669000</v>
       </c>
       <c r="F52" s="3">
-        <v>10857000</v>
+        <v>4895000</v>
       </c>
       <c r="G52" s="3">
-        <v>10045000</v>
+        <v>4628000</v>
       </c>
       <c r="H52" s="3">
-        <v>9101000</v>
+        <v>4765000</v>
       </c>
       <c r="I52" s="3">
-        <v>14140000</v>
+        <v>8437000</v>
       </c>
       <c r="J52" s="3">
-        <v>10169000</v>
+        <v>4799000</v>
       </c>
       <c r="K52" s="3">
         <v>7756000</v>
@@ -2752,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7653000</v>
+        <v>6683000</v>
       </c>
       <c r="E59" s="3">
-        <v>8673000</v>
+        <v>7954000</v>
       </c>
       <c r="F59" s="3">
-        <v>6635000</v>
+        <v>6110000</v>
       </c>
       <c r="G59" s="3">
-        <v>4796000</v>
+        <v>4277000</v>
       </c>
       <c r="H59" s="3">
-        <v>5182000</v>
+        <v>4624000</v>
       </c>
       <c r="I59" s="3">
-        <v>4247000</v>
+        <v>3770000</v>
       </c>
       <c r="J59" s="3">
-        <v>4411000</v>
+        <v>3772000</v>
       </c>
       <c r="K59" s="3">
         <v>4450000</v>
@@ -2842,22 +2843,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>61405000</v>
+        <v>62261000</v>
       </c>
       <c r="E61" s="3">
-        <v>55256000</v>
+        <v>56031000</v>
       </c>
       <c r="F61" s="3">
-        <v>50960000</v>
+        <v>51160000</v>
       </c>
       <c r="G61" s="3">
-        <v>41944000</v>
+        <v>42068000</v>
       </c>
       <c r="H61" s="3">
-        <v>37543000</v>
+        <v>37599000</v>
       </c>
       <c r="I61" s="3">
-        <v>26782000</v>
+        <v>26845000</v>
       </c>
       <c r="J61" s="3">
         <v>31410000</v>
@@ -2887,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>29097000</v>
+        <v>14209000</v>
       </c>
       <c r="E62" s="3">
-        <v>27548000</v>
+        <v>13468000</v>
       </c>
       <c r="F62" s="3">
-        <v>26846000</v>
+        <v>13775000</v>
       </c>
       <c r="G62" s="3">
-        <v>25253000</v>
+        <v>12411000</v>
       </c>
       <c r="H62" s="3">
-        <v>24448000</v>
+        <v>11169000</v>
       </c>
       <c r="I62" s="3">
-        <v>21476000</v>
+        <v>9231000</v>
       </c>
       <c r="J62" s="3">
-        <v>25779000</v>
+        <v>14172000</v>
       </c>
       <c r="K62" s="3">
         <v>25925000</v>
@@ -3067,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>130021000</v>
+        <v>118465000</v>
       </c>
       <c r="E66" s="3">
-        <v>119706000</v>
+        <v>109499000</v>
       </c>
       <c r="F66" s="3">
-        <v>103710000</v>
+        <v>95243000</v>
       </c>
       <c r="G66" s="3">
-        <v>91171000</v>
+        <v>82755000</v>
       </c>
       <c r="H66" s="3">
-        <v>80686000</v>
+        <v>75844000</v>
       </c>
       <c r="I66" s="3">
-        <v>69558000</v>
+        <v>65821000</v>
       </c>
       <c r="J66" s="3">
-        <v>69727000</v>
+        <v>68432000</v>
       </c>
       <c r="K66" s="3">
         <v>65652000</v>
@@ -3695,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6151000</v>
+        <v>5939000</v>
       </c>
       <c r="E83" s="3">
-        <v>4790000</v>
+        <v>4627000</v>
       </c>
       <c r="F83" s="3">
-        <v>4214000</v>
+        <v>4189000</v>
       </c>
       <c r="G83" s="3">
-        <v>4315000</v>
+        <v>4295000</v>
       </c>
       <c r="H83" s="3">
-        <v>4478000</v>
+        <v>4460000</v>
       </c>
       <c r="I83" s="3">
-        <v>4147000</v>
+        <v>4128000</v>
       </c>
       <c r="J83" s="3">
-        <v>2638000</v>
+        <v>2603000</v>
       </c>
       <c r="K83" s="3">
         <v>3428000</v>
@@ -4029,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9548000</v>
+        <v>-25113000</v>
       </c>
       <c r="E91" s="3">
-        <v>-9742000</v>
+        <v>-19283000</v>
       </c>
       <c r="F91" s="3">
-        <v>-7048000</v>
+        <v>-16077000</v>
       </c>
       <c r="G91" s="3">
-        <v>-6747000</v>
+        <v>-14610000</v>
       </c>
       <c r="H91" s="3">
-        <v>-5912000</v>
+        <v>-17462000</v>
       </c>
       <c r="I91" s="3">
-        <v>-6010000</v>
+        <v>-13004000</v>
       </c>
       <c r="J91" s="3">
-        <v>-5445000</v>
+        <v>-10740000</v>
       </c>
       <c r="K91" s="3">
         <v>-4240000</v>
@@ -4228,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3782000</v>
+        <v>3782000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3352000</v>
+        <v>3352000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3024000</v>
+        <v>3024000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2743000</v>
+        <v>2743000</v>
       </c>
       <c r="H96" s="3">
-        <v>-2408000</v>
+        <v>2408000</v>
       </c>
       <c r="I96" s="3">
-        <v>-2101000</v>
+        <v>2101000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1845000</v>
+        <v>1845000</v>
       </c>
       <c r="K96" s="3">
         <v>-1612000</v>

--- a/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>NEE</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24753000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28114000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20956000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17069000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17997000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19204000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16727000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17173000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16138000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17486000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17021000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15136000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14256000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15341000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9886000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10138000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10817000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8508000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7473000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8003000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7062000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7529000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7522000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8588000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8750000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8152000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8276000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9258000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14867000</v>
+      </c>
+      <c r="E10" s="3">
         <v>17976000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10139000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8561000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10524000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11201000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9665000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9644000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8616000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8898000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8271000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6984000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5980000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6083000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-622000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-689000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-27000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-414000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-566000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-465000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3926000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>547000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-305000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>28000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>87000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5462000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5879000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4389000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3924000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4052000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4216000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3911000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2357000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3120000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2831000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2551000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2163000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1518000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1567000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17391000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18037000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17081000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13976000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13034000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13838000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12356000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11190000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11679000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12854000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12637000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11895000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10996000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12116000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7362000</v>
+      </c>
+      <c r="E18" s="3">
         <v>10077000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3875000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3093000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4963000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5366000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4371000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5983000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4459000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4632000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4384000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3241000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3260000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3225000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="E20" s="3">
         <v>154000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-515000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-938000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1166000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-254000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-502000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-704000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1212000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>577000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>458000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1458000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>381000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>262000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13112000</v>
+      </c>
+      <c r="E21" s="3">
         <v>15802000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8779000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7955000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7849000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9836000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8784000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9044000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9099000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8412000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7738000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7220000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5054000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2235000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3324000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>585000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1270000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1950000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2249000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1498000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1558000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1293000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1219000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1197000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2245000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1038000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1035000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6037000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7288000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3832000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3175000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2413000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3836000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7352000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4663000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4378000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3990000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3645000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2454000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2603000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2452000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1006000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>586000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>348000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>44000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>448000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1576000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-660000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1379000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1228000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1176000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>777000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>692000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>529000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5698000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6282000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3246000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2827000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2369000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3388000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5776000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5323000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2999000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2762000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2469000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1677000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1911000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6946000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7310000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4147000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3573000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2919000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3769000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6638000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5380000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2906000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2752000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2465000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1677000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1911000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,27 +1672,30 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>231000</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>288000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-154000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>515000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>938000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1166000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>254000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>502000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>704000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1212000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-577000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-458000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1458000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-381000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6946000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7310000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4147000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3573000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2919000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3769000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6638000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5380000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2906000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2752000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2465000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1908000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1911000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6946000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7310000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4147000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3573000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2919000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3769000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6638000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5380000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2906000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2752000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2465000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1908000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1911000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2690000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1601000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>639000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1105000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>638000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1714000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1292000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>571000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>577000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>438000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>329000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>377000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2078,324 +2167,348 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5164000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6607000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5436000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4108000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2974000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2807000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2969000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2737000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2439000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2265000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2159000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2289000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2056000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1802000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2214000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2106000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1934000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1561000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1552000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1328000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1223000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1273000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1289000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1259000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1292000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1153000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1073000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1074000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2927000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3228000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4519000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2303000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1377000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2262000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1474000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1210000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2389000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2916000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1962000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1779000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1638000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11951000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15361000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13490000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9288000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7382000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7408000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6393000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7181000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7409000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6795000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6944000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5842000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5237000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4872000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>18010000</v>
+      </c>
+      <c r="E47" s="3">
         <v>16467000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15129000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15438000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13787000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14604000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12784000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8324000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7916000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6924000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6565000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6657000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5166000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4774000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>140050000</v>
+      </c>
+      <c r="E48" s="3">
         <v>126612000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>111823000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>100100000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>92466000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>82010000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>70334000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72289000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66912000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>61386000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55705000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>52720000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49413000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42490000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6581000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6783000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5613000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5586000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4947000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4756000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1599000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2051000</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1842000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>614000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>240000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>247000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>262000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6903000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5739000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5669000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4895000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4628000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4765000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8437000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4799000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7756000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5532000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4882000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5789000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4376000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4790000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>190144000</v>
+      </c>
+      <c r="E54" s="3">
         <v>177489000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>158935000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>140912000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>127684000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117691000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103702000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97963000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>89993000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>82479000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74605000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69306000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>64439000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>57188000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6982000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8504000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8312000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6935000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4615000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3631000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2386000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3235000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3447000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2529000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1354000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1281000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1191000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9948000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11806000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9710000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3867000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6147000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5040000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10930000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3615000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3022000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3006000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4657000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4457000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4182000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2157000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7409000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6683000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7954000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6110000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4277000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4624000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3770000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3772000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4450000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4572000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3652000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3532000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3416000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3371000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25355000</v>
+      </c>
+      <c r="E60" s="3">
         <v>27963000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26695000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17437000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15558000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13853000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17563000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11243000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10919000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10107000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9663000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9189000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8879000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6719000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>73612000</v>
+      </c>
+      <c r="E61" s="3">
         <v>62261000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56031000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51160000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42068000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37599000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26845000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31410000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27818000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>26681000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24044000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23969000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23177000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20810000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14973000</v>
+      </c>
+      <c r="E62" s="3">
         <v>14209000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13468000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13775000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12411000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11169000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9231000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14172000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25925000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22579000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20730000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18108000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16315000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14716000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>129283000</v>
+      </c>
+      <c r="E66" s="3">
         <v>118465000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>109499000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>95243000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82755000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>75844000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>65821000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68432000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>65652000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59905000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54689000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51266000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48371000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>42245000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32946000</v>
+      </c>
+      <c r="E72" s="3">
         <v>30235000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>26707000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25911000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25363000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25199000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23837000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19020000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15458000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14140000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12773000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11569000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10783000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9876000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50101000</v>
+      </c>
+      <c r="E76" s="3">
         <v>47468000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39229000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37202000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>36513000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37005000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34144000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28236000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24341000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22574000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19916000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18040000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16068000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14943000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6946000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7310000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4147000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3573000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2919000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3769000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6638000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5380000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2906000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2752000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2465000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1908000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1911000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1923000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5534000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5939000</v>
       </c>
-      <c r="E83" s="3">
-        <v>4627000</v>
-      </c>
       <c r="F83" s="3">
+        <v>4772000</v>
+      </c>
+      <c r="G83" s="3">
         <v>4189000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4295000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4460000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4128000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2603000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3428000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3203000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2896000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2521000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1567000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13260000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11301000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8262000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7553000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7983000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8155000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6593000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6458000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6369000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6116000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5500000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5102000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3992000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4074000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24729000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25113000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19283000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16077000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14610000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17462000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13004000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10740000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4240000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3872000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3503000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3228000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4870000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4027000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22264000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23467000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18359000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13591000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13699000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16177000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10950000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8918000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8046000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8005000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6361000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6123000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5279000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4235000</v>
+      </c>
+      <c r="E96" s="3">
         <v>3782000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3352000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3024000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2743000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2408000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2101000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1845000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1612000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1385000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1261000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1122000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1004000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-920000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,83 +4644,89 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7000000</v>
+      </c>
+      <c r="E100" s="3">
         <v>12149000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12229000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5807000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6174000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3873000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7634000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2888000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2424000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1883000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1130000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1280000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-20000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>26000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>10000</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
@@ -4492,52 +4740,58 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2018000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2125000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-230000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>438000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4145000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3270000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>454000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>757000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>139000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>109000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-48000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>75000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NEE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>NEE</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27412000</v>
+      </c>
+      <c r="E8" s="3">
         <v>24753000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28114000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20956000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17069000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17997000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19204000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16727000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17173000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16138000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17486000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17021000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15136000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14256000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15341000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10343000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9886000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10138000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10817000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8508000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7473000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8003000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7062000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7529000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7522000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8588000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8750000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8152000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8276000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9258000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>17069000</v>
+      </c>
+      <c r="E10" s="3">
         <v>14867000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17976000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10139000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8561000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10524000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11201000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9665000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9644000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8616000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8898000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8271000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6984000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5980000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6083000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-622000</v>
+        <v>-546000</v>
       </c>
       <c r="E14" s="3">
+        <v>-595000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-689000</v>
       </c>
-      <c r="F14" s="3">
-        <v>-27000</v>
-      </c>
       <c r="G14" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H14" s="3">
         <v>-414000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-566000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-465000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3926000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>547000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-305000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>28000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>87000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6580000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5462000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5879000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4389000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3924000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4052000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4216000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3911000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2357000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3120000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2831000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2551000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2163000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1518000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1567000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17391000</v>
+        <v>19125000</v>
       </c>
       <c r="E17" s="3">
+        <v>17364000</v>
+      </c>
+      <c r="F17" s="3">
         <v>18037000</v>
       </c>
-      <c r="F17" s="3">
-        <v>17081000</v>
-      </c>
       <c r="G17" s="3">
+        <v>17029000</v>
+      </c>
+      <c r="H17" s="3">
         <v>13976000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13034000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13838000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12356000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11190000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11679000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12854000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12637000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11895000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10996000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12116000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7362000</v>
+        <v>8287000</v>
       </c>
       <c r="E18" s="3">
+        <v>7389000</v>
+      </c>
+      <c r="F18" s="3">
         <v>10077000</v>
       </c>
-      <c r="F18" s="3">
-        <v>3875000</v>
-      </c>
       <c r="G18" s="3">
+        <v>3927000</v>
+      </c>
+      <c r="H18" s="3">
         <v>3093000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4963000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5366000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4371000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5983000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4459000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4632000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4384000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3241000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3260000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3225000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-269000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-288000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>154000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-515000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-938000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1166000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-254000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-502000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-704000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1212000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>577000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>458000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1458000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>381000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>262000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13112000</v>
+        <v>15136000</v>
       </c>
       <c r="E21" s="3">
+        <v>13139000</v>
+      </c>
+      <c r="F21" s="3">
         <v>15802000</v>
       </c>
-      <c r="F21" s="3">
-        <v>8779000</v>
-      </c>
       <c r="G21" s="3">
+        <v>8831000</v>
+      </c>
+      <c r="H21" s="3">
         <v>7955000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7849000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9836000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8784000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9044000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9099000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8412000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7738000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7220000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5054000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4572000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2235000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3324000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>585000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1270000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1950000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2249000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1498000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1558000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1293000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1219000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1197000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2245000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1038000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1035000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4530000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6037000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7288000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3832000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3175000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2413000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3836000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7352000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4663000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4378000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3990000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3645000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2454000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2603000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2452000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-802000</v>
+      </c>
+      <c r="E24" s="3">
         <v>339000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1006000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>586000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>348000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>44000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>448000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1576000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-660000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1379000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1228000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1176000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>777000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>692000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>529000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5332000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5698000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6282000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3246000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2827000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2369000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3388000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5776000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5323000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2999000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2762000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2469000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1677000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1911000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1923000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6835000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6946000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7310000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4147000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3573000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2919000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3769000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6638000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5380000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2906000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2752000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2465000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1677000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1911000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1923000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,27 +1735,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>231000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E32" s="3">
         <v>288000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-154000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>515000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>938000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1166000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>254000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>502000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>704000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1212000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-577000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-458000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1458000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-381000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-262000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6835000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6946000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7310000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4147000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3573000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2919000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3769000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6638000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5380000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2906000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2752000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2465000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1908000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1911000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1923000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6835000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6946000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7310000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4147000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3573000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2919000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3769000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6638000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5380000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2906000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2752000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2465000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1908000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1911000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1923000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2812000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1487000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2690000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1601000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>639000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1105000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>638000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1714000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1292000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>571000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>577000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>438000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>329000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>377000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2170,345 +2259,369 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5164000</v>
+        <v>6091000</v>
       </c>
       <c r="E43" s="3">
+        <v>4912000</v>
+      </c>
+      <c r="F43" s="3">
         <v>6607000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5436000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4108000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2974000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2807000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2969000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2737000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2439000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2265000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2159000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2289000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2056000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1802000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2420000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2214000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2106000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1934000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1561000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1552000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1328000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1223000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1273000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1289000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1259000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1292000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1153000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1073000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1074000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2927000</v>
+        <v>2067000</v>
       </c>
       <c r="E45" s="3">
+        <v>3179000</v>
+      </c>
+      <c r="F45" s="3">
         <v>3228000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4519000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2303000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1377000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2262000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1474000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1210000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2389000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2916000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1962000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1779000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1638000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13584000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11951000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15361000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13490000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9288000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7382000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7408000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6393000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7181000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7409000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6795000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6944000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5842000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5237000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4872000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19005000</v>
+      </c>
+      <c r="E47" s="3">
         <v>18010000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16467000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15129000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>15438000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>13787000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14604000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12784000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8324000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7916000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6924000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6565000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6657000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5166000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4774000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>157747000</v>
+      </c>
+      <c r="E48" s="3">
         <v>140050000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>126612000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>111823000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>100100000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>92466000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82010000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>70334000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72289000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66912000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>61386000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55705000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52720000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49413000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42490000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6616000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6581000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6783000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5613000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5586000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4947000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4756000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1599000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2051000</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1842000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>614000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>240000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>247000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>262000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7985000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6903000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5739000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5669000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4895000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4628000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4765000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8437000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4799000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7756000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5532000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4882000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5789000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4376000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4790000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212721000</v>
+      </c>
+      <c r="E54" s="3">
         <v>190144000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>177489000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>158935000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>140912000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>127684000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117691000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>103702000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97963000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>89993000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>82479000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74605000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>69306000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>64439000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57188000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7583000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6982000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8504000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8312000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6935000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4615000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3631000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2386000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3235000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3447000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2529000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1354000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1281000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1191000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6063000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9948000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11806000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9710000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3867000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6147000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5040000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10930000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3615000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3022000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3006000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4657000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4457000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4182000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2157000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7986000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7409000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6683000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7954000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6110000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4277000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4624000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3770000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3772000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4450000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4572000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3652000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3532000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3416000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3371000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22817000</v>
+      </c>
+      <c r="E60" s="3">
         <v>25355000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27963000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26695000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17437000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15558000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13853000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17563000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11243000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10919000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10107000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9663000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9189000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8879000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6719000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>91157000</v>
+      </c>
+      <c r="E61" s="3">
         <v>73612000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62261000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>56031000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51160000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42068000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37599000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26845000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31410000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27818000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26681000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24044000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23969000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23177000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20810000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16561000</v>
+      </c>
+      <c r="E62" s="3">
         <v>14973000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14209000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13468000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13775000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12411000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11169000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9231000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14172000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25925000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22579000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20730000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18108000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16315000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14716000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>146242000</v>
+      </c>
+      <c r="E66" s="3">
         <v>129283000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>118465000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>109499000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>95243000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>82755000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75844000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>65821000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68432000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65652000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>59905000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54689000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51266000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>48371000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>42245000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>35102000</v>
+      </c>
+      <c r="E72" s="3">
         <v>32946000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30235000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26707000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25911000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25363000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25199000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23837000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19020000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15458000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14140000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12773000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11569000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10783000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9876000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>54608000</v>
+      </c>
+      <c r="E76" s="3">
         <v>50101000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47468000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>39229000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37202000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36513000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>37005000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34144000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28236000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24341000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22574000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19916000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18040000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16068000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14943000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6835000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6946000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7310000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4147000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3573000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2919000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3769000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6638000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5380000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2906000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2752000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2465000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1908000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1911000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1923000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5609000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5534000</v>
       </c>
-      <c r="E83" s="3">
-        <v>5939000</v>
-      </c>
       <c r="F83" s="3">
+        <v>6093000</v>
+      </c>
+      <c r="G83" s="3">
         <v>4772000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4189000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4295000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4460000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4128000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2603000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3428000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3203000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2896000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2521000</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1567000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12485000</v>
+      </c>
+      <c r="E89" s="3">
         <v>13260000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11301000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8262000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7553000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7983000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8155000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6593000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6458000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6369000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6116000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5500000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5102000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3992000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4074000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24606000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24729000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25113000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19283000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16077000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14610000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17462000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13004000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10740000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4240000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3872000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3503000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3228000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4870000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4027000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23865000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22264000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23467000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18359000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13591000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13699000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16177000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10950000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8918000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8046000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8005000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6361000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6123000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5279000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4680000</v>
+      </c>
+      <c r="E96" s="3">
         <v>4235000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3782000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3352000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3024000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2743000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2408000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2101000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1845000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1612000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1385000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1261000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1122000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1004000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-920000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,89 +4889,95 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12979000</v>
+      </c>
+      <c r="E100" s="3">
         <v>7000000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12149000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12229000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5807000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6174000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3873000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7634000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2888000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2424000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1883000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1000000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1130000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1280000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-20000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>26000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>10000</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
@@ -4743,55 +4991,61 @@
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2018000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2125000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-230000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>438000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4145000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3270000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>454000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>757000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>139000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>75000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
